--- a/public/templates/process-docs/场地平整检验批质量验收记录.xlsx
+++ b/public/templates/process-docs/场地平整检验批质量验收记录.xlsx
@@ -56,13 +56,13 @@
     <t xml:space="preserve">施工单位</t>
   </si>
   <si>
-    <t xml:space="preserve">中核华辰建筑工程有限公司</t>
+    <t xml:space="preserve">{{施工单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">项目负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">谢智敏</t>
+    <t xml:space="preserve">{{施工单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">检验批容量</t>
@@ -74,14 +74,14 @@
     <t xml:space="preserve">分包单位</t>
   </si>
   <si>
-    <t xml:space="preserve">河南誉华美建设工程有限公司</t>
+    <t xml:space="preserve">{{分包单位}}</t>
   </si>
   <si>
     <t xml:space="preserve">分包单位项目
 负责人</t>
   </si>
   <si>
-    <t xml:space="preserve">胡彦芳</t>
+    <t xml:space="preserve">{{分包单位项目负责人}}</t>
   </si>
   <si>
     <t xml:space="preserve">检验批部位</t>
